--- a/datos/indicadores_adelantados/transporte/flujo_ferroviario_1999_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/flujo_ferroviario_1999_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\TRANSPORTE\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Estadisticas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4A6447-7E6E-4EA8-AE42-DF3681A636F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE2D79E-45B7-426E-8F41-7121CA885A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="27">
   <si>
     <t>PERIODO</t>
   </si>
@@ -987,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U399"/>
+  <dimension ref="B1:U400"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="2" customWidth="1"/>
@@ -9962,22 +9962,22 @@
         <v>26</v>
       </c>
       <c r="C384" s="22">
-        <v>5365</v>
+        <v>6627</v>
       </c>
       <c r="D384" s="22">
-        <v>387102.40099999995</v>
+        <v>460180.66399999987</v>
       </c>
       <c r="E384" s="22">
         <v>0</v>
       </c>
       <c r="F384" s="22">
-        <v>3059</v>
+        <v>6391</v>
       </c>
       <c r="G384" s="22">
-        <v>827404.3</v>
+        <v>1042953.0099999999</v>
       </c>
       <c r="H384" s="16">
-        <v>192.7</v>
+        <v>233.3</v>
       </c>
       <c r="P384" s="27"/>
       <c r="Q384" s="27"/>
@@ -10003,7 +10003,7 @@
         <v>435</v>
       </c>
       <c r="G385" s="21">
-        <v>127975.68000000002</v>
+        <v>127975.68000000001</v>
       </c>
       <c r="H385" s="15">
         <v>45.550000000000004</v>
@@ -10032,7 +10032,7 @@
         <v>38</v>
       </c>
       <c r="G386" s="21">
-        <v>101340.75000000001</v>
+        <v>101340.75</v>
       </c>
       <c r="H386" s="15">
         <v>18.61</v>
@@ -10061,7 +10061,7 @@
         <v>295</v>
       </c>
       <c r="G387" s="21">
-        <v>133445.66999999998</v>
+        <v>133445.67000000001</v>
       </c>
       <c r="H387" s="15">
         <v>19.760000000000002</v>
@@ -10090,7 +10090,7 @@
         <v>318</v>
       </c>
       <c r="G388" s="21">
-        <v>146505.07999999999</v>
+        <v>146505.07999999996</v>
       </c>
       <c r="H388" s="15">
         <v>43.089999999999996</v>
@@ -10160,14 +10160,28 @@
       <c r="T390" s="27"/>
       <c r="U390" s="27"/>
     </row>
-    <row r="391" spans="2:21" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B391" s="26"/>
-      <c r="C391" s="23"/>
-      <c r="D391" s="23"/>
-      <c r="E391" s="24"/>
-      <c r="F391" s="23"/>
-      <c r="G391" s="23"/>
-      <c r="H391" s="24"/>
+    <row r="391" spans="2:21" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B391" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C391" s="21">
+        <v>1262</v>
+      </c>
+      <c r="D391" s="21">
+        <v>73078.26299999989</v>
+      </c>
+      <c r="E391" s="15">
+        <v>0</v>
+      </c>
+      <c r="F391" s="21">
+        <v>3332</v>
+      </c>
+      <c r="G391" s="21">
+        <v>215548.71</v>
+      </c>
+      <c r="H391" s="15">
+        <v>40.600000000000009</v>
+      </c>
       <c r="P391" s="27"/>
       <c r="Q391" s="27"/>
       <c r="R391" s="27"/>
@@ -10175,51 +10189,66 @@
       <c r="T391" s="27"/>
       <c r="U391" s="27"/>
     </row>
-    <row r="392" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B392" s="19" t="s">
+    <row r="392" spans="2:21" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B392" s="26"/>
+      <c r="C392" s="23"/>
+      <c r="D392" s="23"/>
+      <c r="E392" s="24"/>
+      <c r="F392" s="23"/>
+      <c r="G392" s="23"/>
+      <c r="H392" s="24"/>
+      <c r="P392" s="27"/>
+      <c r="Q392" s="27"/>
+      <c r="R392" s="27"/>
+      <c r="S392" s="27"/>
+      <c r="T392" s="27"/>
+      <c r="U392" s="27"/>
+    </row>
+    <row r="393" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B393" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C392" s="18"/>
-      <c r="D392" s="18"/>
-      <c r="E392" s="18"/>
-      <c r="F392" s="18"/>
-      <c r="G392" s="18"/>
-      <c r="H392" s="18"/>
-    </row>
-    <row r="393" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B393" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C393" s="11"/>
+      <c r="C393" s="18"/>
+      <c r="D393" s="18"/>
+      <c r="E393" s="18"/>
+      <c r="F393" s="18"/>
+      <c r="G393" s="18"/>
+      <c r="H393" s="18"/>
     </row>
     <row r="394" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B394" s="20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C394" s="11"/>
-      <c r="H394" s="5"/>
     </row>
     <row r="395" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B395" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C395" s="11"/>
+      <c r="H395" s="5"/>
+    </row>
+    <row r="396" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B396" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C395" s="11"/>
-    </row>
-    <row r="396" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B396" s="17"/>
       <c r="C396" s="11"/>
     </row>
     <row r="397" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B397" s="17"/>
-      <c r="C397" s="14"/>
+      <c r="C397" s="11"/>
     </row>
     <row r="398" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B398" s="12"/>
+      <c r="B398" s="17"/>
       <c r="C398" s="14"/>
     </row>
     <row r="399" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B399" s="12"/>
-      <c r="C399" s="13"/>
+      <c r="C399" s="14"/>
+    </row>
+    <row r="400" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B400" s="12"/>
+      <c r="C400" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/datos/indicadores_adelantados/transporte/flujo_ferroviario_1999_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/flujo_ferroviario_1999_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\TRANSPORTE\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Estadisticas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE2D79E-45B7-426E-8F41-7121CA885A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C30D93E-EDA1-4C1E-A0FE-A1931AE8CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="27">
   <si>
     <t>PERIODO</t>
   </si>
@@ -987,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U400"/>
+  <dimension ref="B1:U401"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="2" customWidth="1"/>
@@ -9962,22 +9962,22 @@
         <v>26</v>
       </c>
       <c r="C384" s="22">
-        <v>6627</v>
+        <v>7655</v>
       </c>
       <c r="D384" s="22">
-        <v>460180.66399999987</v>
+        <v>505990.16899999982</v>
       </c>
       <c r="E384" s="22">
         <v>0</v>
       </c>
       <c r="F384" s="22">
-        <v>6391</v>
+        <v>8365</v>
       </c>
       <c r="G384" s="22">
-        <v>1042953.0099999999</v>
+        <v>1252624.4300000002</v>
       </c>
       <c r="H384" s="16">
-        <v>233.3</v>
+        <v>264.99</v>
       </c>
       <c r="P384" s="27"/>
       <c r="Q384" s="27"/>
@@ -9994,7 +9994,7 @@
         <v>1552</v>
       </c>
       <c r="D385" s="21">
-        <v>58109.211999999985</v>
+        <v>58109.21200000005</v>
       </c>
       <c r="E385" s="15">
         <v>0</v>
@@ -10003,10 +10003,10 @@
         <v>435</v>
       </c>
       <c r="G385" s="21">
-        <v>127975.68000000001</v>
+        <v>127975.68000000002</v>
       </c>
       <c r="H385" s="15">
-        <v>45.550000000000004</v>
+        <v>45.55</v>
       </c>
       <c r="P385" s="27"/>
       <c r="Q385" s="27"/>
@@ -10023,7 +10023,7 @@
         <v>699</v>
       </c>
       <c r="D386" s="21">
-        <v>69322.491000000053</v>
+        <v>69322.490999999907</v>
       </c>
       <c r="E386" s="15">
         <v>0</v>
@@ -10032,7 +10032,7 @@
         <v>38</v>
       </c>
       <c r="G386" s="21">
-        <v>101340.75</v>
+        <v>101340.75000000001</v>
       </c>
       <c r="H386" s="15">
         <v>18.61</v>
@@ -10061,7 +10061,7 @@
         <v>295</v>
       </c>
       <c r="G387" s="21">
-        <v>133445.67000000001</v>
+        <v>133445.66999999998</v>
       </c>
       <c r="H387" s="15">
         <v>19.760000000000002</v>
@@ -10090,7 +10090,7 @@
         <v>318</v>
       </c>
       <c r="G388" s="21">
-        <v>146505.07999999996</v>
+        <v>146505.07999999999</v>
       </c>
       <c r="H388" s="15">
         <v>43.089999999999996</v>
@@ -10110,7 +10110,7 @@
         <v>672</v>
       </c>
       <c r="D389" s="21">
-        <v>60445.57</v>
+        <v>60445.569999999898</v>
       </c>
       <c r="E389" s="15">
         <v>0</v>
@@ -10139,7 +10139,7 @@
         <v>894</v>
       </c>
       <c r="D390" s="21">
-        <v>62445.526999999973</v>
+        <v>62445.527000000067</v>
       </c>
       <c r="E390" s="15">
         <v>0</v>
@@ -10168,7 +10168,7 @@
         <v>1262</v>
       </c>
       <c r="D391" s="21">
-        <v>73078.26299999989</v>
+        <v>73078.263000000035</v>
       </c>
       <c r="E391" s="15">
         <v>0</v>
@@ -10177,10 +10177,10 @@
         <v>3332</v>
       </c>
       <c r="G391" s="21">
-        <v>215548.71</v>
+        <v>215548.70999999996</v>
       </c>
       <c r="H391" s="15">
-        <v>40.600000000000009</v>
+        <v>40.6</v>
       </c>
       <c r="P391" s="27"/>
       <c r="Q391" s="27"/>
@@ -10189,14 +10189,28 @@
       <c r="T391" s="27"/>
       <c r="U391" s="27"/>
     </row>
-    <row r="392" spans="2:21" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B392" s="26"/>
-      <c r="C392" s="23"/>
-      <c r="D392" s="23"/>
-      <c r="E392" s="24"/>
-      <c r="F392" s="23"/>
-      <c r="G392" s="23"/>
-      <c r="H392" s="24"/>
+    <row r="392" spans="2:21" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B392" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392" s="21">
+        <v>1028</v>
+      </c>
+      <c r="D392" s="21">
+        <v>45809.504999999932</v>
+      </c>
+      <c r="E392" s="15">
+        <v>0</v>
+      </c>
+      <c r="F392" s="21">
+        <v>1974</v>
+      </c>
+      <c r="G392" s="21">
+        <v>209671.42000000007</v>
+      </c>
+      <c r="H392" s="15">
+        <v>31.689999999999998</v>
+      </c>
       <c r="P392" s="27"/>
       <c r="Q392" s="27"/>
       <c r="R392" s="27"/>
@@ -10204,51 +10218,66 @@
       <c r="T392" s="27"/>
       <c r="U392" s="27"/>
     </row>
-    <row r="393" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B393" s="19" t="s">
+    <row r="393" spans="2:21" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B393" s="26"/>
+      <c r="C393" s="23"/>
+      <c r="D393" s="23"/>
+      <c r="E393" s="24"/>
+      <c r="F393" s="23"/>
+      <c r="G393" s="23"/>
+      <c r="H393" s="24"/>
+      <c r="P393" s="27"/>
+      <c r="Q393" s="27"/>
+      <c r="R393" s="27"/>
+      <c r="S393" s="27"/>
+      <c r="T393" s="27"/>
+      <c r="U393" s="27"/>
+    </row>
+    <row r="394" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B394" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C393" s="18"/>
-      <c r="D393" s="18"/>
-      <c r="E393" s="18"/>
-      <c r="F393" s="18"/>
-      <c r="G393" s="18"/>
-      <c r="H393" s="18"/>
-    </row>
-    <row r="394" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B394" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C394" s="11"/>
+      <c r="C394" s="18"/>
+      <c r="D394" s="18"/>
+      <c r="E394" s="18"/>
+      <c r="F394" s="18"/>
+      <c r="G394" s="18"/>
+      <c r="H394" s="18"/>
     </row>
     <row r="395" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B395" s="20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C395" s="11"/>
-      <c r="H395" s="5"/>
     </row>
     <row r="396" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B396" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C396" s="11"/>
+      <c r="H396" s="5"/>
+    </row>
+    <row r="397" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B397" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C396" s="11"/>
-    </row>
-    <row r="397" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B397" s="17"/>
       <c r="C397" s="11"/>
     </row>
     <row r="398" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B398" s="17"/>
-      <c r="C398" s="14"/>
+      <c r="C398" s="11"/>
     </row>
     <row r="399" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B399" s="12"/>
+      <c r="B399" s="17"/>
       <c r="C399" s="14"/>
     </row>
     <row r="400" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B400" s="12"/>
-      <c r="C400" s="13"/>
+      <c r="C400" s="14"/>
+    </row>
+    <row r="401" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B401" s="12"/>
+      <c r="C401" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
